--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.90539502340799</v>
+        <v>6.484626691303799</v>
       </c>
       <c r="D2" t="n">
-        <v>39.23744072195833</v>
+        <v>6.376084117318229</v>
       </c>
       <c r="E2" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F2" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.76585472556918</v>
+        <v>5.649451392904993</v>
       </c>
       <c r="D3" t="n">
-        <v>34.26582207763067</v>
+        <v>5.568196087614983</v>
       </c>
       <c r="E3" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F3" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.23957219177096</v>
+        <v>6.051430481162781</v>
       </c>
       <c r="D4" t="n">
-        <v>36.35867553573996</v>
+        <v>5.908284774557743</v>
       </c>
       <c r="E4" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F4" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.2934454324001</v>
+        <v>6.547684882765016</v>
       </c>
       <c r="D5" t="n">
-        <v>39.23145741786497</v>
+        <v>6.375111830403057</v>
       </c>
       <c r="E5" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F5" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.67422610442952</v>
+        <v>5.147061741969797</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76405102636075</v>
+        <v>5.324158291783622</v>
       </c>
       <c r="E6" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F6" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19170801715509</v>
+        <v>3.443652552787702</v>
       </c>
       <c r="D7" t="n">
-        <v>20.25131077041569</v>
+        <v>3.29083800019255</v>
       </c>
       <c r="E7" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F7" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.37195740952908</v>
+        <v>3.635443079048475</v>
       </c>
       <c r="D8" t="n">
-        <v>23.49395678381153</v>
+        <v>3.817767977369374</v>
       </c>
       <c r="E8" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F8" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.67627629017172</v>
+        <v>4.497394897152905</v>
       </c>
       <c r="D9" t="n">
-        <v>26.53690459414926</v>
+        <v>4.312246996549254</v>
       </c>
       <c r="E9" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F9" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.78351175613602</v>
+        <v>2.402320660372103</v>
       </c>
       <c r="D10" t="n">
-        <v>15.08759971049323</v>
+        <v>2.45173495295515</v>
       </c>
       <c r="E10" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F10" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.09179909842955</v>
+        <v>3.264917353494802</v>
       </c>
       <c r="D11" t="n">
-        <v>19.56645984276187</v>
+        <v>3.179549724448804</v>
       </c>
       <c r="E11" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F11" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.65774282390792</v>
+        <v>5.306883208885038</v>
       </c>
       <c r="D12" t="n">
-        <v>33.57438322088326</v>
+        <v>5.455837273393529</v>
       </c>
       <c r="E12" t="n">
-        <v>8.284930581703625</v>
+        <v>1.346301219526839</v>
       </c>
       <c r="F12" t="n">
-        <v>8.100276618328406</v>
+        <v>1.316294950478366</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
